--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90866FAE-1253-4A5D-92BB-A18D2EF7488A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19FD30D-F351-4ACA-829F-A97ED5FA3927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="682">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -626,9 +626,6 @@
   </si>
   <si>
     <t>помогать из процентов, которые даёт эта сумма</t>
-  </si>
-  <si>
-    <t>помогать их лихвы, которую дают этот денежный общак</t>
   </si>
   <si>
     <t>приносили положительные моменты</t>
@@ -1380,9 +1377,6 @@
     <t>выработка схемы покушения была отложена до момента определения графика появления</t>
   </si>
   <si>
-    <t>выработка замысла покушения был отложен до мгновения определения расписания и появляения</t>
-  </si>
-  <si>
     <t>этот «пресс»</t>
   </si>
   <si>
@@ -2051,6 +2045,78 @@
   </si>
   <si>
     <t>количества денежных средств для взятого долга в рост</t>
+  </si>
+  <si>
+    <t>«медведковской» банде</t>
+  </si>
+  <si>
+    <t>«медведковскойм» преступном сообществе</t>
+  </si>
+  <si>
+    <t>получил на долгое время приличный процент</t>
+  </si>
+  <si>
+    <t>получил на долгое время приличную лихву</t>
+  </si>
+  <si>
+    <t>выработка замысла покушения была отложена до мгновения определения расписания и появляения</t>
+  </si>
+  <si>
+    <t>помогать из лихвы, которую дают этот денежный общак</t>
+  </si>
+  <si>
+    <t>включилась давно ожидаемая, отработанная схема</t>
+  </si>
+  <si>
+    <t>включился давно ожидаемый, отработанный исход</t>
+  </si>
+  <si>
+    <t>новой «фигурой», которую</t>
+  </si>
+  <si>
+    <t>новым «человеком», которого</t>
+  </si>
+  <si>
+    <t>почерневший от высокой температуры асфальт</t>
+  </si>
+  <si>
+    <t>почерневшее от высокого уровня тепла твёрдое дорожное покрытие</t>
+  </si>
+  <si>
+    <t>фурор покушении</t>
+  </si>
+  <si>
+    <t>фурор покушения</t>
+  </si>
+  <si>
+    <t>дружественных «бригад»</t>
+  </si>
+  <si>
+    <t>союзных «бригад»</t>
+  </si>
+  <si>
+    <t>борбуна-классика</t>
+  </si>
+  <si>
+    <t>борбу́на-исконника</t>
+  </si>
+  <si>
+    <t>а в казино рядом,</t>
+  </si>
+  <si>
+    <t>а в игорное заведение рядом,</t>
+  </si>
+  <si>
+    <t>, принятый на общем «собрании»</t>
+  </si>
+  <si>
+    <t>, принятое на общем «собрании»</t>
+  </si>
+  <si>
+    <t>в случае случайной</t>
+  </si>
+  <si>
+    <t>в случае непредвиденной</t>
   </si>
 </sst>
 </file>
@@ -2107,7 +2173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -2130,6 +2196,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2433,7 +2500,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -2481,7 +2548,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -2622,10 +2689,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -2678,10 +2745,10 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -2694,10 +2761,10 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -2729,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
@@ -2738,26 +2805,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2770,10 +2837,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2802,26 +2869,26 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>395</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -2829,15 +2896,15 @@
         <v>90</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -2850,18 +2917,18 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>337</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -2874,34 +2941,34 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>335</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>399</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -2922,26 +2989,26 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>383</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -2954,74 +3021,74 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>308</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -3034,10 +3101,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>310</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -3045,7 +3112,7 @@
         <v>99</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
@@ -3058,10 +3125,10 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -3106,42 +3173,42 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>262</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -3157,7 +3224,7 @@
         <v>116</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -3202,10 +3269,10 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -3234,10 +3301,10 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>294</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -3253,23 +3320,23 @@
         <v>135</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>379</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -3282,10 +3349,10 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -3293,7 +3360,7 @@
         <v>138</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -3306,10 +3373,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -3322,34 +3389,34 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>407</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>304</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -3362,10 +3429,10 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -3378,66 +3445,66 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -3450,18 +3517,18 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
@@ -3474,10 +3541,10 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -3498,10 +3565,10 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -3514,18 +3581,18 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -3546,18 +3613,18 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B102" s="7" t="s">
         <v>401</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -3586,34 +3653,34 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B108" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B109" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>250</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -3634,10 +3701,10 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>355</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -3674,50 +3741,50 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>381</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>292</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -3725,367 +3792,383 @@
         <v>191</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>192</v>
+        <v>663</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B128" s="7" t="s">
         <v>314</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B130" s="7" t="s">
         <v>365</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B131" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B132" s="7" t="s">
         <v>403</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B134" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B137" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B138" s="7" t="s">
         <v>351</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B141" s="7" t="s">
         <v>298</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B144" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="B147" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B148" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B154" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B155" s="7" t="s">
         <v>316</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B158" s="7" t="s">
         <v>326</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B162" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B166" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>430</v>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A170" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A171" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -4109,90 +4192,90 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -4204,7 +4287,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
@@ -4213,578 +4296,578 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>436</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>361</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>296</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>280</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>375</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -4829,34 +4912,90 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>303</v>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>658</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -4867,7 +5006,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
@@ -4876,205 +5015,221 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C8" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B24" s="13" t="s">
         <v>636</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" s="12" t="s">
-        <v>638</v>
-      </c>
-      <c r="C24" s="12"/>
+      <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>655</v>
+        <v>653</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>681</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19FD30D-F351-4ACA-829F-A97ED5FA3927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160AD74B-0B15-4429-9B17-680D215D386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -2640,7 +2640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
@@ -2751,25 +2751,25 @@
         <v>617</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>76</v>
+        <v>632</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="B16" s="5" t="s">
         <v>633</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B17">
-    <sortCondition ref="A1:A17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B16">
+    <sortCondition ref="A1:A16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4287,7 +4287,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
@@ -4302,699 +4302,699 @@
         <v>427</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>434</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>662</v>
+        <v>435</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>442</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>627</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>483</v>
+      <c r="A30" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>487</v>
+      <c r="A32" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>489</v>
+      <c r="A33" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>490</v>
+        <v>386</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>386</v>
+        <v>493</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B37" s="6" t="s">
         <v>498</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>506</v>
+      <c r="A42" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>508</v>
+      <c r="A43" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>535</v>
+        <v>595</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>596</v>
+        <v>597</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>600</v>
+      <c r="A47" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>649</v>
+      <c r="A55" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>202</v>
+      <c r="A57" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>361</v>
+      <c r="A58" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>204</v>
+      <c r="A59" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
-        <v>352</v>
+        <v>589</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>353</v>
+        <v>590</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>589</v>
+        <v>295</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>590</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
-        <v>295</v>
+        <v>613</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>296</v>
+        <v>614</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
-        <v>613</v>
+        <v>562</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>614</v>
+        <v>563</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>563</v>
+      <c r="A64" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
-        <v>279</v>
+        <v>209</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>280</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>212</v>
+      <c r="A68" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>300</v>
+      <c r="A69" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>230</v>
+      <c r="A72" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>375</v>
+      <c r="A73" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>184</v>
+      <c r="A75" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>186</v>
+      <c r="A76" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="5" t="s">
-        <v>265</v>
+      <c r="A79" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>302</v>
+      <c r="A80" t="s">
+        <v>658</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>658</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>659</v>
+      <c r="A81" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
-        <v>566</v>
+        <v>615</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>567</v>
+        <v>616</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>616</v>
+      <c r="A83" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B89" s="1" t="s">
         <v>679</v>
       </c>
     </row>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160AD74B-0B15-4429-9B17-680D215D386E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3514BBC9-0A8E-4280-AC90-759EF7A4D2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3514BBC9-0A8E-4280-AC90-759EF7A4D2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B06144B-D201-4D67-9955-EDF713D22BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
     <sheet name="Составные" sheetId="3" r:id="rId2"/>
     <sheet name="простые" sheetId="8" r:id="rId3"/>
-    <sheet name="неизменные" sheetId="4" r:id="rId4"/>
-    <sheet name="неизменные_длинные" sheetId="5" r:id="rId5"/>
-    <sheet name="неизменные_короткие" sheetId="6" r:id="rId6"/>
+    <sheet name="неизменные_короткие" sheetId="6" r:id="rId4"/>
+    <sheet name="неизменные" sheetId="4" r:id="rId5"/>
+    <sheet name="неизменные_длинные" sheetId="5" r:id="rId6"/>
     <sheet name="ошибки" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">неизменные!$A$1:$B$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">неизменные!$A$1:$B$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="706">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -2117,6 +2117,78 @@
   </si>
   <si>
     <t>в случае непредвиденной</t>
+  </si>
+  <si>
+    <t>Жене сыну</t>
+  </si>
+  <si>
+    <t>Жене и сыну</t>
+  </si>
+  <si>
+    <t>академию ГРУ, расположенную</t>
+  </si>
+  <si>
+    <t>высшее учебное заведение ГРУ, расположенное</t>
+  </si>
+  <si>
+    <t>Карты по задачам формируемой группы были раскрыты все</t>
+  </si>
+  <si>
+    <t>Расклад по задачам образуемого подразделения были раскрыты все</t>
+  </si>
+  <si>
+    <t>прибывающих и убывающих объектов</t>
+  </si>
+  <si>
+    <t>прибывающих и убывающих лиц и средств передвижения</t>
+  </si>
+  <si>
+    <t>пробивалась настойчивая фраза, повторенная</t>
+  </si>
+  <si>
+    <t>пробивалось настойчивое выражение, повторенное</t>
+  </si>
+  <si>
+    <t>Резко ослабели члены</t>
+  </si>
+  <si>
+    <t>????</t>
+  </si>
+  <si>
+    <t>По дороге сюда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По дороге сюда, </t>
+  </si>
+  <si>
+    <t>возглавляющих нашу «структуру»</t>
+  </si>
+  <si>
+    <t>возглавляющих нашу «дружину»</t>
+  </si>
+  <si>
+    <t>«ореховский» авторитет</t>
+  </si>
+  <si>
+    <t>«ореховская» личная значимость</t>
+  </si>
+  <si>
+    <t>конторская «наружка»</t>
+  </si>
+  <si>
+    <t>наружное наблюдение ФСБ</t>
+  </si>
+  <si>
+    <t>дальнее расстоянии</t>
+  </si>
+  <si>
+    <t>дальнее расстояние</t>
+  </si>
+  <si>
+    <t>аудио-и</t>
+  </si>
+  <si>
+    <t>аудио- и</t>
   </si>
 </sst>
 </file>
@@ -2795,11 +2867,778 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B171"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B94"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.7265625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>658</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>701</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B172"/>
+  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="58" style="5" customWidth="1"/>
     <col min="2" max="2" width="55.81640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4169,6 +5008,14 @@
       </c>
       <c r="B171" s="5" t="s">
         <v>669</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A172" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>
@@ -4181,7 +5028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4285,728 +5132,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.81640625" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>658</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="5" customWidth="1"/>
@@ -5232,6 +5360,46 @@
         <v>681</v>
       </c>
     </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>705</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B24:C24"/>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B06144B-D201-4D67-9955-EDF713D22BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903BE2C1-307B-4844-A8FE-98B9B3127672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
-    <sheet name="Составные" sheetId="3" r:id="rId2"/>
-    <sheet name="простые" sheetId="8" r:id="rId3"/>
-    <sheet name="неизменные_короткие" sheetId="6" r:id="rId4"/>
-    <sheet name="неизменные" sheetId="4" r:id="rId5"/>
-    <sheet name="неизменные_длинные" sheetId="5" r:id="rId6"/>
-    <sheet name="ошибки" sheetId="7" r:id="rId7"/>
+    <sheet name="запятые" sheetId="9" r:id="rId2"/>
+    <sheet name="Составные" sheetId="3" r:id="rId3"/>
+    <sheet name="простые" sheetId="8" r:id="rId4"/>
+    <sheet name="неизменные_короткие" sheetId="6" r:id="rId5"/>
+    <sheet name="неизменные" sheetId="4" r:id="rId6"/>
+    <sheet name="неизменные_длинные" sheetId="5" r:id="rId7"/>
+    <sheet name="ошибки" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">неизменные!$A$1:$B$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">неизменные!$A$1:$B$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -214,9 +215,6 @@
     <t>пускаясь по извилистым дорогам</t>
   </si>
   <si>
-    <t xml:space="preserve">горного серпантина </t>
-  </si>
-  <si>
     <t>горных извилистых дорог</t>
   </si>
   <si>
@@ -2189,6 +2187,9 @@
   </si>
   <si>
     <t>аудио- и</t>
+  </si>
+  <si>
+    <t>горного серпантина</t>
   </si>
 </sst>
 </file>
@@ -2465,254 +2466,261 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A2:B29"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="48.1796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>657</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>26</v>
+      <c r="A14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>34</v>
+      <c r="A18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>622</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>656</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="A29" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B22" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B29">
+    <sortCondition ref="A2:A29"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8ABEC4-23C3-4C68-A6C0-21892A6ACD18}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="31.7265625" customWidth="1"/>
+    <col min="2" max="2" width="94.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
@@ -2721,122 +2729,130 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>633</v>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2848,17 +2864,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C830F-D298-443C-B559-8038A360E6EC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +2882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B94"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2877,754 +2893,754 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>497</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>501</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>507</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>595</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>601</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>643</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>645</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B57" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>352</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="B60" s="7" t="s">
         <v>589</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>295</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>613</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>562</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>374</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>301</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>657</v>
+      </c>
+      <c r="B80" s="12" t="s">
         <v>658</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>566</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>684</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B91" s="10" t="s">
         <v>690</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>696</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -3633,9 +3649,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B172"/>
+  <dimension ref="A1:B173"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="58" style="5" customWidth="1"/>
@@ -3644,1378 +3660,1386 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>548</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>394</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>338</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>546</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>336</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>334</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>307</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>574</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>321</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>273</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>390</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>378</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B75" s="7" t="s">
         <v>396</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>556</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>580</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>544</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>285</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B90" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="B91" s="7" t="s">
         <v>558</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="B93" s="7" t="s">
         <v>587</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>329</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B102" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="B107" s="7" t="s">
         <v>539</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B108" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B109" s="7" t="s">
         <v>368</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>354</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B115" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B118" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>253</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B120" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="B123" s="7" t="s">
         <v>542</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B126" s="7" t="s">
         <v>552</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B128" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B130" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B131" s="7" t="s">
         <v>327</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B132" s="7" t="s">
         <v>402</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B134" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B135" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B137" s="7" t="s">
         <v>358</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B138" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B140" s="7" t="s">
         <v>550</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B141" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>346</v>
-      </c>
-      <c r="B142" s="7" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="B143" s="7" t="s">
         <v>536</v>
-      </c>
-      <c r="B143" s="7" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B144" s="7" t="s">
         <v>376</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B147" s="7" t="s">
         <v>404</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B148" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="B152" s="7" t="s">
         <v>554</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="B153" s="7" t="s">
         <v>578</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B154" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B155" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B158" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B162" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B164" s="7" t="s">
         <v>576</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B166" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>650</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="B168" s="10" t="s">
         <v>654</v>
-      </c>
-      <c r="B168" s="10" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B170" s="5" t="s">
         <v>660</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>668</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B172" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="B172" s="10" t="s">
-        <v>687</v>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A173" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5028,7 +5052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5039,90 +5063,90 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -5132,7 +5156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5143,261 +5167,261 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>515</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>520</v>
-      </c>
       <c r="C8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>521</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>524</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>526</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>528</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>532</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>583</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>585</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>591</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>607</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>634</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>637</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>639</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>641</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>652</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>670</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>680</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>682</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>692</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>694</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>702</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>704</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903BE2C1-307B-4844-A8FE-98B9B3127672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB27A39-51F7-4B54-9B6A-E1116B1DF80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -2496,6 +2496,14 @@
         <v>11</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>33</v>
@@ -2638,6 +2646,22 @@
       </c>
       <c r="B23" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -2658,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8ABEC4-23C3-4C68-A6C0-21892A6ACD18}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.7265625" customWidth="1"/>
@@ -2713,6 +2737,14 @@
         <v>51</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2720,37 +2752,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A4:B16"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>69</v>
@@ -2775,28 +2783,12 @@
         <v>568</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -2884,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.7265625" style="1" customWidth="1"/>
@@ -3641,6 +3633,14 @@
       </c>
       <c r="B94" s="1" t="s">
         <v>700</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шерстобитов.xlsx
+++ b/словари/шерстобитов.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB27A39-51F7-4B54-9B6A-E1116B1DF80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A22A517-3189-4E09-BD55-C73644AE252F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="697" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
-    <sheet name="запятые" sheetId="9" r:id="rId2"/>
-    <sheet name="Составные" sheetId="3" r:id="rId3"/>
-    <sheet name="простые" sheetId="8" r:id="rId4"/>
-    <sheet name="неизменные_короткие" sheetId="6" r:id="rId5"/>
-    <sheet name="неизменные" sheetId="4" r:id="rId6"/>
-    <sheet name="неизменные_длинные" sheetId="5" r:id="rId7"/>
-    <sheet name="ошибки" sheetId="7" r:id="rId8"/>
+    <sheet name="составные_длинные" sheetId="10" r:id="rId2"/>
+    <sheet name="запятые" sheetId="9" r:id="rId3"/>
+    <sheet name="Составные" sheetId="3" r:id="rId4"/>
+    <sheet name="простые" sheetId="8" r:id="rId5"/>
+    <sheet name="неизменные_короткие" sheetId="6" r:id="rId6"/>
+    <sheet name="неизменные" sheetId="4" r:id="rId7"/>
+    <sheet name="неизменные_длинные" sheetId="5" r:id="rId8"/>
+    <sheet name="ошибки" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">неизменные!$A$1:$B$191</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">неизменные!$A$1:$B$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">неизменные_длинные!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Составные_важные!$A$1:$B$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="704">
   <si>
     <t>обрабатываемой информации, по просторам которой</t>
   </si>
@@ -651,12 +652,6 @@
   </si>
   <si>
     <t>пять палат,</t>
-  </si>
-  <si>
-    <t>с новой «фигурой»</t>
-  </si>
-  <si>
-    <t>с новым «человеком»</t>
   </si>
   <si>
     <t>с разными «командами»</t>
@@ -2473,35 +2468,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
+      <c r="A2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>43</v>
+      <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2513,27 +2508,27 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
+      <c r="A7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -2554,114 +2549,74 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>621</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>47</v>
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>17</v>
+      <c r="A16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
@@ -2681,6 +2636,52 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C32ED4EE-8EF4-445A-BD01-03821CA72A9F}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39.1796875" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8ABEC4-23C3-4C68-A6C0-21892A6ACD18}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2750,113 +2751,113 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A4:B16"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.1796875" style="5" customWidth="1"/>
     <col min="2" max="2" width="27.7265625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>565</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>70</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>74</v>
+      <c r="A5" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>568</v>
+      <c r="A6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>58</v>
+      <c r="A8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>59</v>
+        <v>615</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>60</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B16">
-    <sortCondition ref="A1:A16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B13">
+    <sortCondition ref="A1:A13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76C830F-D298-443C-B559-8038A360E6EC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2874,7 +2875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B95"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2885,434 +2886,434 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -3324,83 +3325,83 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>203</v>
+      <c r="A58" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
-        <v>351</v>
+        <v>586</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>352</v>
+        <v>587</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
-        <v>588</v>
+        <v>292</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>589</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>294</v>
+        <v>610</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>295</v>
+        <v>611</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
-        <v>612</v>
+        <v>559</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>613</v>
+        <v>560</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>562</v>
+      <c r="A63" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>205</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>279</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
@@ -3412,27 +3413,27 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>211</v>
+      <c r="A67" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>299</v>
+      <c r="A68" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -3444,99 +3445,99 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>229</v>
+      <c r="A71" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>374</v>
+      <c r="A72" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>183</v>
+      <c r="A74" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>185</v>
+      <c r="A75" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
-        <v>264</v>
+      <c r="A78" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>301</v>
+      <c r="A79" t="s">
+        <v>655</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>657</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>658</v>
+      <c r="A80" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>615</v>
+      <c r="A82" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -3549,10 +3550,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -3581,34 +3582,34 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="10" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>690</v>
+        <v>693</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -3628,19 +3629,19 @@
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>700</v>
+      <c r="A94" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>66</v>
+      <c r="A95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -3649,7 +3650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B173"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3660,26 +3661,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -3692,10 +3693,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -3724,26 +3725,26 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -3751,15 +3752,15 @@
         <v>89</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -3772,18 +3773,18 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -3796,34 +3797,34 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -3844,26 +3845,26 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -3876,74 +3877,74 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
@@ -3956,10 +3957,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -3967,7 +3968,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
@@ -3980,10 +3981,10 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -4028,42 +4029,42 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
@@ -4079,7 +4080,7 @@
         <v>115</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
@@ -4124,10 +4125,10 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -4156,10 +4157,10 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
@@ -4175,23 +4176,23 @@
         <v>134</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
@@ -4204,10 +4205,10 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
@@ -4215,7 +4216,7 @@
         <v>137</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -4228,10 +4229,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
@@ -4244,34 +4245,34 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
@@ -4284,10 +4285,10 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -4300,66 +4301,66 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -4372,18 +4373,18 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="29" x14ac:dyDescent="0.35">
@@ -4396,10 +4397,10 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -4420,10 +4421,10 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -4436,18 +4437,18 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -4468,18 +4469,18 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -4508,34 +4509,34 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -4556,10 +4557,10 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -4596,50 +4597,50 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -4647,23 +4648,23 @@
         <v>190</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -4676,10 +4677,10 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -4692,26 +4693,26 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -4724,18 +4725,18 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -4743,295 +4744,295 @@
         <v>197</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B168" s="10" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -5052,7 +5053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5063,90 +5064,90 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -5156,7 +5157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5167,261 +5168,261 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C8" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" s="13" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
